--- a/data/Vaudreuil_Acquisition_Leads.xlsx
+++ b/data/Vaudreuil_Acquisition_Leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Acquisition Leads'!$A$1:$Q$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Acquisition Leads'!$A$1:$Q$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1040,12 +1040,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Gâteau signé M Inc</t>
+          <t>Les Toitures Deslauriers Inc.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>578 Avenue Saint-Charles unité 7, Vaudreuil-Dorion</t>
+          <t>556 Rue Jetté, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1056,17 +1056,17 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>http://www.gateausignem.com/</t>
+          <t>http://www.deslaurierscouvreurawestisland.ca/</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>(438) 523-0176</t>
+          <t>(514) 886-9501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Claude Gauthier</t>
+          <t>Luc Morin</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Roofing Contractor</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1110,23 +1110,23 @@
         </is>
       </c>
       <c r="P7" s="5" t="n">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Roofing Contractor | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Annie's Beauty Bar Inc</t>
+          <t>Déménagement Mancuso Transport Inc</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3187 Route Harwood Unit N, Vaudreuil-Dorion</t>
+          <t>Autoroute du Souvenir, Pincourt</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1137,37 +1137,37 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://www.anniesbeautybarinc.com/</t>
+          <t>https://mancusotransport.com/</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>(450) 319-0146</t>
+          <t>(514) 775-6975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Michel Lavoie</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Transportation / Logistics</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1191,23 +1191,23 @@
         </is>
       </c>
       <c r="P8" s="5" t="n">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Hôpital Vétérinaire De L'Île-Perrot inc.</t>
+          <t>Allegiant 3D Design &amp; Manufacturing Inc.</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>400 Grand Boulevard, L'Île-Perrot</t>
+          <t>169 Rue Joseph-Carrier, Vaudreuil-Dorion, QC J7V 3V1, Canada</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1218,17 +1218,17 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://veterinaireileperrot.com/</t>
+          <t>http://allegiant3d.com/</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>(514) 453-3406</t>
+          <t>(450) 218-4004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Robert Lavoie</t>
+          <t>Pierre Morin</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Light Manufacturing</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$123K-$255K</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1272,23 +1272,23 @@
         </is>
       </c>
       <c r="P9" s="5" t="n">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Light Manufacturing | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Les Toitures Deslauriers Inc.</t>
+          <t>Paysagiste Stone Inc</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>556 Rue Jetté, Vaudreuil-Dorion</t>
+          <t>760 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>http://www.deslaurierscouvreurawestisland.ca/</t>
+          <t>http://www.stoneinc.ca/</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>(514) 886-9501</t>
+          <t>(450) 424-9441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Luc Morin</t>
+          <t>Michel Bouchard</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>landscaping</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Roofing Contractor</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1353,23 +1353,23 @@
         </is>
       </c>
       <c r="P10" s="5" t="n">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>Category: Roofing Contractor | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: Landscaping | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Déménagement Mancuso Transport Inc</t>
+          <t>Les Industries André inc.</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Autoroute du Souvenir, Pincourt</t>
+          <t>290 Rue Rodolphe-Besner, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1380,37 +1380,37 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://mancusotransport.com/</t>
+          <t>http://www.portedegarageandre.com/ca/fr/?utm_source=GoogleMyBusiness&amp;utm_medium=GoogleMyBusiness&amp;utm_campaign=LIMMO</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>(514) 775-6975</t>
+          <t>(450) 455-3585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Claude Bouchard</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Logistics</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1434,23 +1434,23 @@
         </is>
       </c>
       <c r="P11" s="5" t="n">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Allegiant 3D Design &amp; Manufacturing Inc.</t>
+          <t>Ecoplus Inc.</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>169 Rue Joseph-Carrier, Vaudreuil-Dorion, QC J7V 3V1, Canada</t>
+          <t>1205 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1461,37 +1461,37 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>http://allegiant3d.com/</t>
+          <t>http://www.ecopluspro.com/</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>(450) 218-4004</t>
+          <t>(514) 895-5862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Pierre Morin</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Light Manufacturing</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.2M-$2.5M</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>$123K-$255K</t>
+          <t>$180K-$374K</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1515,23 +1515,23 @@
         </is>
       </c>
       <c r="P12" s="5" t="n">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>Category: Light Manufacturing | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Paysagiste Stone Inc</t>
+          <t>CR Usinage Inc.</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>760 Route Harwood, Vaudreuil-Dorion</t>
+          <t>260 Rue Rodolphe-Besner, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1542,37 +1542,37 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>http://www.stoneinc.ca/</t>
+          <t>http://crusinage.com/</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-9441</t>
+          <t>(450) 218-6341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Michel Bouchard</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>landscaping</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Precision Manufacturing</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1596,23 +1596,23 @@
         </is>
       </c>
       <c r="P13" s="5" t="n">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Category: Landscaping | High acquisition fit; priority follow-up</t>
+          <t>Category: Precision Manufacturing | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Les Industries André inc.</t>
+          <t>SOUDURE A &amp; D INC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>290 Rue Rodolphe-Besner, Vaudreuil-Dorion</t>
+          <t>562 Grand Boulevard, L'Île-Perrot</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1623,27 +1623,27 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>http://www.portedegarageandre.com/ca/fr/?utm_source=GoogleMyBusiness&amp;utm_medium=GoogleMyBusiness&amp;utm_campaign=LIMMO</t>
+          <t>http://souduread.com/</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-3585</t>
+          <t>(514) 453-9774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Claude Bouchard</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Metal Fabrication</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1677,23 +1677,23 @@
         </is>
       </c>
       <c r="P14" s="5" t="n">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: Metal Fabrication | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ecoplus Inc.</t>
+          <t>Toitures Poirier et Fils inc</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1205 Route Harwood, Vaudreuil-Dorion</t>
+          <t>1041 Route Harwood lcoal 3, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>http://www.ecopluspro.com/</t>
+          <t>http://toiturespoirier.ca/</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>(514) 895-5862</t>
+          <t>(450) 455-1643</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Roofing Contractor</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1758,23 +1758,23 @@
         </is>
       </c>
       <c r="P15" s="5" t="n">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Roofing Contractor | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CR Usinage Inc.</t>
+          <t>Groupe Deluxe - Entrepreneur général Pincourt</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>260 Rue Rodolphe-Besner, Vaudreuil-Dorion</t>
+          <t>13 Avenue de la Promenade, Pincourt</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>http://crusinage.com/</t>
+          <t>https://www.411habitation.com/renovations/monteregie/pincourt-2/renovations-pincourt.htm</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>(450) 218-6341</t>
+          <t>(514) 238-5071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Precision Manufacturing</t>
+          <t>General Contractor</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$112K-$233K</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1839,23 +1839,23 @@
         </is>
       </c>
       <c r="P16" s="5" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>Category: Precision Manufacturing | High acquisition fit; priority follow-up</t>
+          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SOUDURE A &amp; D INC</t>
+          <t>Camlew Solutions Inc</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>562 Grand Boulevard, L'Île-Perrot</t>
+          <t>1111 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>http://souduread.com/</t>
+          <t>https://camlewsolutions.com/</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>(514) 453-9774</t>
+          <t>(450) 455-8080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Metal Fabrication</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.1M-$2.2M</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$161K-$334K</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1920,23 +1920,23 @@
         </is>
       </c>
       <c r="P17" s="5" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>Category: Metal Fabrication | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Toitures Poirier et Fils inc</t>
+          <t>Clôtures Raymond Inc</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1041 Route Harwood lcoal 3, Vaudreuil-Dorion</t>
+          <t>412 Boulevard Harwood suite 211, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>http://toiturespoirier.ca/</t>
+          <t>https://www.cloturesraymond.ca/</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-1643</t>
+          <t>(450) 424-3820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Roofing Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.5M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>$180K-$374K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2001,23 +2001,23 @@
         </is>
       </c>
       <c r="P18" s="5" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>Category: Roofing Contractor | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Groupe Deluxe - Entrepreneur général Pincourt</t>
+          <t>Radiateurs d'Auto Willard Inc (Les)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>13 Avenue de la Promenade, Pincourt</t>
+          <t>1205 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2028,37 +2028,37 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://www.411habitation.com/renovations/monteregie/pincourt-2/renovations-pincourt.htm</t>
+          <t>https://radiateurswillard.ca/</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>(514) 238-5071</t>
+          <t>(450) 455-7963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Marc Gauthier</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>General Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.3M-$2.6M</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>$112K-$233K</t>
+          <t>$190K-$395K</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2082,23 +2082,23 @@
         </is>
       </c>
       <c r="P19" s="5" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Camlew Solutions Inc</t>
+          <t>Brabant Construction Inc</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1111 Route Harwood, Vaudreuil-Dorion</t>
+          <t>520 Av. Saint-Charles, Vaudreuil-Dorion, QC J7V 8V9, Canada</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2109,37 +2109,37 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://camlewsolutions.com/</t>
+          <t>https://www.brabantconstruction.ca/</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-8080</t>
+          <t>(450) 455-4927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>André Tremblay</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>General Contractor</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.2M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>$161K-$334K</t>
+          <t>$102K-$213K</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2163,23 +2163,23 @@
         </is>
       </c>
       <c r="P20" s="5" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Clôtures Raymond Inc</t>
+          <t>Mini-Entrepot Henault Inc</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>412 Boulevard Harwood suite 211, Vaudreuil-Dorion</t>
+          <t>277 Rue Boisvert, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2190,27 +2190,27 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://www.cloturesraymond.ca/</t>
+          <t>http://entreposages.com/</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-3820</t>
+          <t>(450) 455-3205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Marc Lavoie</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Warehousing / Distribution</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2244,23 +2244,23 @@
         </is>
       </c>
       <c r="P21" s="5" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Radiateurs d'Auto Willard Inc (Les)</t>
+          <t>Plomberie Robert Proulx Inc</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1205 Route Harwood, Vaudreuil-Dorion</t>
+          <t>102 Boulevard Don-Quichotte, L'Île-Perrot</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2269,29 +2269,25 @@
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>https://radiateurswillard.ca/</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-7963</t>
+          <t>(514) 453-4332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Marc Gauthier</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2301,7 +2297,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Plumbing Contractor</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2311,12 +2307,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.2M-$2.5M</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$183K-$380K</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2325,23 +2321,23 @@
         </is>
       </c>
       <c r="P22" s="5" t="n">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Brabant Construction Inc</t>
+          <t>Fondation B &amp; B Inc</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>520 Av. Saint-Charles, Vaudreuil-Dorion, QC J7V 8V9, Canada</t>
+          <t>2920 Rue du Meunier, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2352,17 +2348,17 @@
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://www.brabantconstruction.ca/</t>
+          <t>http://www.fondationsbb.com/</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-4927</t>
+          <t>(514) 386-5851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>André Tremblay</t>
+          <t>Michel Tremblay</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2377,12 +2373,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>General Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2392,12 +2388,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>$102K-$213K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2406,23 +2402,23 @@
         </is>
       </c>
       <c r="P23" s="5" t="n">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Mini-Entrepot Henault Inc</t>
+          <t>Aqua Data inc.</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>277 Rue Boisvert, Vaudreuil-Dorion</t>
+          <t>330 Rue Joseph-Carrier, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2433,17 +2429,17 @@
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>http://entreposages.com/</t>
+          <t>http://www.aquadata.com/</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-3205</t>
+          <t>(514) 425-1010</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Marc Lavoie</t>
+          <t>Marc Roy</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2463,7 +2459,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Warehousing / Distribution</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2473,12 +2469,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.1M-$2.2M</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$161K-$334K</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2487,23 +2483,23 @@
         </is>
       </c>
       <c r="P24" s="5" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Plomberie Robert Proulx Inc</t>
+          <t>Plomberie Dominion Inc</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>102 Boulevard Don-Quichotte, L'Île-Perrot</t>
+          <t>1801 Rue Chicoine, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2512,25 +2508,25 @@
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>(514) 453-4332</t>
-        </is>
-      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>https://plomberiedominion.ca/</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Jean Gagnon</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2550,12 +2546,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.5M</t>
+          <t>$1.1M-$2.2M</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>$183K-$380K</t>
+          <t>$161K-$334K</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2564,7 +2560,7 @@
         </is>
       </c>
       <c r="P25" s="5" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
@@ -2575,12 +2571,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Fondation B &amp; B Inc</t>
+          <t>Pièces d’Auto L.S. Inc.</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2920 Rue du Meunier, Vaudreuil-Dorion</t>
+          <t>80 Route de Lotbinière, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2591,27 +2587,27 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>http://www.fondationsbb.com/</t>
+          <t>http://www.lsautopart.com/</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>(514) 386-5851</t>
+          <t>(450) 455-5741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Michel Tremblay</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2631,12 +2627,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.3M-$2.6M</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$190K-$395K</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2645,7 +2641,7 @@
         </is>
       </c>
       <c r="P26" s="5" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
@@ -2656,12 +2652,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Aqua Data inc.</t>
+          <t>Arseneault Bourbonnais Inc</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>330 Rue Joseph-Carrier, Vaudreuil-Dorion</t>
+          <t>21 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2672,27 +2668,27 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>http://www.aquadata.com/</t>
+          <t>https://abag.qc.ca/</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>(514) 425-1010</t>
+          <t>(450) 455-6151</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Marc Roy</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2712,12 +2708,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.2M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>$161K-$334K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2726,7 +2722,7 @@
         </is>
       </c>
       <c r="P27" s="5" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
@@ -2737,12 +2733,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SQDC - Pincourt</t>
+          <t>Réfrigération Frigo-Zone Inc. (Réfrigération Vaudreuil-Dorion)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>101 Boulevard Cardinal Léger, Pincourt</t>
+          <t>1995 Montée Labossière, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2753,27 +2749,27 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://www.sqdc.ca/fr-CA/Magasins/s-pincourt/77060</t>
+          <t>https://www.frigozone.com/</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>(514) 646-8003</t>
+          <t>(514) 901-4414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Michel Gauthier</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2793,12 +2789,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2807,7 +2803,7 @@
         </is>
       </c>
       <c r="P28" s="5" t="n">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
@@ -2818,12 +2814,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Plomberie Dominion Inc</t>
+          <t>Solutions Trexo Inc</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1801 Rue Chicoine, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
+          <t>240 Avenue Loyola-Schmidt local 100, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2834,13 +2830,17 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://plomberiedominion.ca/</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+          <t>https://www.trexo.ca/</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>(514) 457-1414</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Jean Gagnon</t>
+          <t>Luc Bouchard</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Plumbing Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2870,37 +2870,37 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.2M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>$161K-$334K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>30+ years</t>
         </is>
       </c>
       <c r="P29" s="5" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Pièces d’Auto L.S. Inc.</t>
+          <t>Robert Daoust &amp; Fils inc.</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>80 Route de Lotbinière, Vaudreuil-Dorion</t>
+          <t>2117 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>http://www.lsautopart.com/</t>
+          <t>http://www.robertdaoustetfils.com/</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-5741</t>
+          <t>(450) 458-4340</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.2M-$2.5M</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$180K-$374K</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2965,23 +2965,23 @@
         </is>
       </c>
       <c r="P30" s="5" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Arseneault Bourbonnais Inc</t>
+          <t>Massawa Auto Inc</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>21 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
+          <t>607 Rue Chicoine, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2992,27 +2992,27 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://abag.qc.ca/</t>
+          <t>http://massawaauto.ca/</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-6151</t>
+          <t>(514) 296-0653</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Luc Gauthier</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.2M-$2.5M</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$180K-$374K</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="P31" s="5" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
@@ -3057,12 +3057,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Réfrigération Frigo-Zone Inc. (Réfrigération Vaudreuil-Dorion)</t>
+          <t>Montreal Ouest Motors Inc.</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1995 Montée Labossière, Vaudreuil-Dorion</t>
+          <t>55 Route de Lotbinière, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://www.frigozone.com/</t>
+          <t>http://www.mtlouestmotors.com/</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>(514) 901-4414</t>
+          <t>(450) 455-1567</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Michel Gauthier</t>
+          <t>Luc Roy</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.3M-$2.6M</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$190K-$395K</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="P32" s="5" t="n">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
@@ -3138,12 +3138,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Solutions Trexo Inc</t>
+          <t>XTL Transport Inc</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>240 Avenue Loyola-Schmidt local 100, Vaudreuil-Dorion</t>
+          <t>2350 Rue Henry-Ford, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3154,17 +3154,17 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>https://www.trexo.ca/</t>
+          <t>https://www.xtl.com/</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>(514) 457-1414</t>
+          <t>(514) 636-1499</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Luc Bouchard</t>
+          <t>André Gagnon</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Transportation / Logistics</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3194,37 +3194,37 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>30+ years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P33" s="5" t="n">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NORMAND NADEAU T.V. INC.</t>
+          <t>Les services Inspec-thor inc.</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>17 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
+          <t>3048 Rue Labelle, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3235,27 +3235,27 @@
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>http://koodomobile.com/</t>
+          <t>http://www.inspec-thor.com/</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>(450) 218-6242</t>
+          <t>(866) 617-8467</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Jean Gauthier</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3275,37 +3275,37 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.5M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>$180K-$374K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P34" s="5" t="n">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Robert Daoust &amp; Fils inc.</t>
+          <t>Lagacé Électrique Inc</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2117 Route Harwood, Vaudreuil-Dorion</t>
+          <t>2881 Rue du Meunier, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3316,27 +3316,27 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>http://www.robertdaoustetfils.com/</t>
+          <t>http://www.lagaceelectrique.com/</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>(450) 458-4340</t>
+          <t>(450) 510-1414</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Jean Roy</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3370,23 +3370,23 @@
         </is>
       </c>
       <c r="P35" s="5" t="n">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Massawa Auto Inc</t>
+          <t>Autotek Inc - Atelier de réparation automobile à Saint-Lazare QC</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>607 Rue Chicoine, Vaudreuil-Dorion</t>
+          <t>490 Route de la Cité-des-Jeunes, Saint-Lazare</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3397,17 +3397,17 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>http://massawaauto.ca/</t>
+          <t>http://www.autotekstlazare.com/</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>(514) 296-0653</t>
+          <t>(450) 424-0763</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Luc Gauthier</t>
+          <t>Marc Gagnon</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3437,21 +3437,21 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.5M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>$180K-$374K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P36" s="5" t="n">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
@@ -3462,12 +3462,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Raylobec Inc</t>
+          <t>Vaudreuil Inc. Heating.</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>325 Rue Marie-Curie, Vaudreuil-Dorion</t>
+          <t>1041 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3478,17 +3478,17 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://www.wasteconnectionscanada.com/raylobec</t>
+          <t>http://www.chauffagevaudreuil.com/</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-0060</t>
+          <t>(450) 455-9845</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>André Bouchard</t>
+          <t>Luc Lavoie</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3518,21 +3518,21 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.2M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>$161K-$334K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P37" s="5" t="n">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
@@ -3543,12 +3543,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Montreal Ouest Motors Inc.</t>
+          <t>Duct Masters Inc. - Air Duct Cleaning Specialist</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>55 Route de Lotbinière, Vaudreuil-Dorion</t>
+          <t>3050 Boulevard de la Gare Suite 221, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3559,17 +3559,17 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>http://www.mtlouestmotors.com/</t>
+          <t>http://www.ductmasters.ca/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-1567</t>
+          <t>(514) 826-7223</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Luc Roy</t>
+          <t>André Côté</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>cleaning_services</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Cleaning Services</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3599,37 +3599,37 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>$1.3M-$2.6M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>$190K-$395K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P38" s="5" t="n">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Cleaning Services | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>XTL Transport Inc</t>
+          <t>PSP CORP.</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2350 Rue Henry-Ford, Vaudreuil-Dorion</t>
+          <t>85 Autoroute 20, L'Île-Perrot</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://www.xtl.com/</t>
+          <t>http://www.pspcorp.ca/?utm_source=GMB&amp;utm_medium=organic&amp;utm_campaign=gmb-website</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>(514) 636-1499</t>
+          <t>(514) 767-6625</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>André Gagnon</t>
+          <t>Claude Gauthier</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Logistics</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3694,23 +3694,23 @@
         </is>
       </c>
       <c r="P39" s="5" t="n">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Les services Inspec-thor inc.</t>
+          <t>Les Services de Béton Universel Ltée (Entrepôt / Warehouse)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>3048 Rue Labelle, Vaudreuil-Dorion</t>
+          <t>1801 Rue Chicoine Local # 6, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3721,27 +3721,27 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>http://www.inspec-thor.com/</t>
+          <t>https://beton-montreal.ca/</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>(866) 617-8467</t>
+          <t>(855) 613-4773</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Luc Gauthier</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Warehousing / Distribution</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$165K-$343K</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3775,23 +3775,23 @@
         </is>
       </c>
       <c r="P40" s="5" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Lagacé Électrique Inc</t>
+          <t>Couvre-Planchers Pincourt</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2881 Rue du Meunier, Vaudreuil-Dorion</t>
+          <t>84 5e Avenue, Pincourt</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>http://www.lagaceelectrique.com/</t>
+          <t>http://www.plancherspincourt.ca/</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>(450) 510-1414</t>
+          <t>(514) 453-7947</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Jean Roy</t>
+          <t>Robert Gauthier</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3842,21 +3842,21 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.5M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>$180K-$374K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P41" s="5" t="n">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
@@ -3867,12 +3867,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Autotek Inc - Atelier de réparation automobile à Saint-Lazare QC</t>
+          <t>Unitrail Inc / Trailgo Wholesale</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>490 Route de la Cité-des-Jeunes, Saint-Lazare</t>
+          <t>3500 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3883,17 +3883,17 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>http://www.autotekstlazare.com/</t>
+          <t>http://trailgo.ca/</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-0763</t>
+          <t>(450) 424-6660</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Marc Gagnon</t>
+          <t>Pierre Tremblay</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>wholesale</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Wholesale / Distribution</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$66K-$137K</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3937,23 +3937,23 @@
         </is>
       </c>
       <c r="P42" s="5" t="n">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Wholesale / Distribution | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Vaudreuil Inc. Heating.</t>
+          <t>Transport Evergreen Reeds</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1041 Route Harwood, Vaudreuil-Dorion</t>
+          <t>980 Rue Valois, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3964,37 +3964,37 @@
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>http://www.chauffagevaudreuil.com/</t>
+          <t>https://www.transportevergreenreeds.com/</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-9845</t>
+          <t>(450) 319-0198</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Luc Lavoie</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Transportation / Logistics</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -4014,27 +4014,27 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>10-15 years</t>
         </is>
       </c>
       <c r="P43" s="5" t="n">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Duct Masters Inc. - Air Duct Cleaning Specialist</t>
+          <t>Habitations Raymond Allard Inc et Groupe F A A Construction</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>3050 Boulevard de la Gare Suite 221, Vaudreuil-Dorion</t>
+          <t>456 Avenue Saint-Charles Local 200, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>http://www.ductmasters.ca/</t>
+          <t>https://www.groupefaa.ca/</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>(514) 826-7223</t>
+          <t>(450) 424-2425</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>André Côté</t>
+          <t>Luc Roy</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>cleaning_services</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Cleaning Services</t>
+          <t>General Contractor</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$110K-$229K</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4099,23 +4099,23 @@
         </is>
       </c>
       <c r="P44" s="5" t="n">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>Category: Cleaning Services | High acquisition fit; priority follow-up</t>
+          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>PSP CORP.</t>
+          <t>LOB Inc</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>85 Autoroute 20, L'Île-Perrot</t>
+          <t>640 Rue Chicoine, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4126,17 +4126,17 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>http://www.pspcorp.ca/?utm_source=GMB&amp;utm_medium=organic&amp;utm_campaign=gmb-website</t>
+          <t>https://www.lob.ca/</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>(514) 767-6625</t>
+          <t>(514) 684-2626</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Claude Gauthier</t>
+          <t>Jean Bouchard</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -4166,21 +4166,21 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.1M-$2.2M</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$161K-$334K</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P45" s="5" t="n">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
@@ -4191,12 +4191,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Les Services de Béton Universel Ltée (Entrepôt / Warehouse)</t>
+          <t>Roland Bourbonnais Plomberie Chauffage</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1801 Rue Chicoine Local # 6, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
+          <t>25 Rue Huot, Notre-Dame-de-l'Île-Perrot, QC J7W 1M3, Canada</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4207,27 +4207,27 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://beton-montreal.ca/</t>
+          <t>https://www.rbourbonnais.ca/</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>(855) 613-4773</t>
+          <t>(514) 453-3578</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Luc Gauthier</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Warehousing / Distribution</t>
+          <t>Plumbing Contractor</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4247,37 +4247,37 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>$165K-$343K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>10-15 years</t>
         </is>
       </c>
       <c r="P46" s="5" t="n">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up | Strong independent ownership signals</t>
+          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Couvre-Planchers Pincourt</t>
+          <t>Insignia Transport Inc</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>84 5e Avenue, Pincourt</t>
+          <t>11 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4288,17 +4288,17 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>http://www.plancherspincourt.ca/</t>
+          <t>http://www.insigniatransport.ca/</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>(514) 453-7947</t>
+          <t>(514) 733-1555</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Robert Gauthier</t>
+          <t>Michel Bouchard</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Transportation / Logistics</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$926K-$1.9M</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$139K-$289K</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -4342,23 +4342,23 @@
         </is>
       </c>
       <c r="P47" s="5" t="n">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Retro Accounting Inc.</t>
+          <t>Electrinstal Inc.</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>330 Rue Lorne-Worsley, Vaudreuil-Dorion</t>
+          <t>523 Rue Renaissance, Pincourt</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>http://www.retroaccounting.com/</t>
+          <t>http://www.electrinstal.ca/</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>(514) 947-7008</t>
+          <t>(514) 713-2747</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Accounting / Financial Services</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4423,23 +4423,23 @@
         </is>
       </c>
       <c r="P48" s="5" t="n">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>Category: Accounting / Financial Services | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Beauté élégante Inc</t>
+          <t>Moreno International Logistics Inc.</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>105 Avenue Saint-Charles #101, Vaudreuil-Dorion</t>
+          <t>1000 Rue Émile-Bouchard, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4448,15 +4448,19 @@
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>http://www.morenointl.com/</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>(450) 218-2003</t>
+          <t>(877) 292-6134</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Robert Gagnon</t>
+          <t>André Gagnon</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4471,12 +4475,12 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Warehousing / Distribution</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4486,12 +4490,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>$173K-$358K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -4500,23 +4504,23 @@
         </is>
       </c>
       <c r="P49" s="5" t="n">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Unitrail Inc / Trailgo Wholesale</t>
+          <t>Peinture Jdp Inc</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>3500 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
+          <t>190 5e Avenue, Pincourt</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4527,17 +4531,17 @@
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>http://trailgo.ca/</t>
+          <t>https://www.411habitation.com/peintres/monteregie/pincourt-3/peintres-pincourt.htm</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-6660</t>
+          <t>(514) 497-1926</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Pierre Tremblay</t>
+          <t>Michel Bouchard</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4552,12 +4556,12 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>wholesale</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Wholesale / Distribution</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4572,32 +4576,32 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>$66K-$137K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P50" s="5" t="n">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>Category: Wholesale / Distribution | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Transport Evergreen Reeds</t>
+          <t>Landevel Inc</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>980 Rue Valois, Vaudreuil-Dorion</t>
+          <t>522 Rue Renaissance, Pincourt</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4608,12 +4612,12 @@
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://www.transportevergreenreeds.com/</t>
+          <t>http://www.landevel.com/</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>(450) 319-0198</t>
+          <t>(514) 425-6660</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4633,12 +4637,12 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Logistics</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4648,37 +4652,37 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>10-15 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P51" s="5" t="n">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Habitations Raymond Allard Inc et Groupe F A A Construction</t>
+          <t>Plomberie CPL Inc.</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>456 Avenue Saint-Charles Local 200, Vaudreuil-Dorion</t>
+          <t>39 Avenue Pasold, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4689,37 +4693,37 @@
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://www.groupefaa.ca/</t>
+          <t>http://plomberiecpl.ca/</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-2425</t>
+          <t>(450) 455-0791</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Luc Roy</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>general</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>General Contractor</t>
+          <t>Plumbing Contractor</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4729,37 +4733,37 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>$110K-$229K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P52" s="5" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LOB Inc</t>
+          <t>Entreprises Hans Gruenwald Inc</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>640 Rue Chicoine, Vaudreuil-Dorion</t>
+          <t>3756 Chem. des Sables, Vaudreuil-Dorion, QC J7V 0K1, Canada</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4770,17 +4774,17 @@
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>https://www.lob.ca/</t>
+          <t>https://www.gruenwald.ca/</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>(514) 684-2626</t>
+          <t>(450) 458-7014</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Jean Bouchard</t>
+          <t>Jean Morin</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4810,12 +4814,12 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.2M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>$161K-$334K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -4824,7 +4828,7 @@
         </is>
       </c>
       <c r="P53" s="5" t="n">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
@@ -4835,12 +4839,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Roland Bourbonnais Plomberie Chauffage</t>
+          <t>BRS Express Inc.</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>25 Rue Huot, Notre-Dame-de-l'Île-Perrot, QC J7W 1M3, Canada</t>
+          <t>384 Rue Chicoine, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4851,27 +4855,27 @@
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://www.rbourbonnais.ca/</t>
+          <t>https://www.brsexpress.com/</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>(514) 453-3578</t>
+          <t>(450) 455-5055</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>André Gagnon</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4881,7 +4885,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Plumbing Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4901,27 +4905,27 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10-15 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P54" s="5" t="n">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Insignia Transport Inc</t>
+          <t>Muscle Mate Equipment Ltd</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11 Boulevard de la Cité-des-Jeunes, Vaudreuil-Dorion</t>
+          <t>3041 Rue du Plateau, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4932,17 +4936,17 @@
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>http://www.insigniatransport.ca/</t>
+          <t>https://www.musclemateworks.com/</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>(514) 733-1555</t>
+          <t>(450) 455-8030</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Michel Bouchard</t>
+          <t>Luc Lavoie</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4957,12 +4961,12 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>equipment_rental</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Transportation / Logistics</t>
+          <t>Equipment / Maintenance</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -4972,37 +4976,37 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>$926K-$1.9M</t>
+          <t>$1.0M-$2.1M</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>$139K-$289K</t>
+          <t>$154K-$319K</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P55" s="5" t="n">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>Category: Transportation / Logistics | High acquisition fit; priority follow-up</t>
+          <t>Category: Equipment / Maintenance | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Electrinstal Inc.</t>
+          <t>Solaris Chem Inc.</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>523 Rue Renaissance, Pincourt</t>
+          <t>3650 Boulevard de la Cité-des-Jeunes Suite 101-102, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5013,27 +5017,27 @@
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>http://www.electrinstal.ca/</t>
+          <t>http://www.solarischem.com/</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>(514) 713-2747</t>
+          <t>(579) 217-0260</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Pierre Bouchard</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -5067,7 +5071,7 @@
         </is>
       </c>
       <c r="P56" s="5" t="n">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
@@ -5078,12 +5082,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Universe Collectibles Inc.</t>
+          <t>Mécano Plus Vaudreuil Inc</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>555a Avenue Saint-Charles, Vaudreuil-Dorion</t>
+          <t>1559 Montée Labossière, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5092,19 +5096,15 @@
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Universe-Collectibles-Inc-101471329145999</t>
-        </is>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>(514) 458-0822</t>
+          <t>(450) 424-4624</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>André Gauthier</t>
+          <t>Pierre Gagnon</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -5134,21 +5134,21 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>$1.2M-$2.4M</t>
+          <t>$1.2M-$2.5M</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>$176K-$364K</t>
+          <t>$183K-$380K</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15-20 years</t>
+          <t>20-30 years</t>
         </is>
       </c>
       <c r="P57" s="5" t="n">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
@@ -5159,12 +5159,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Moreno International Logistics Inc.</t>
+          <t>Entrepreneur Michel Levesque Inc</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1000 Rue Émile-Bouchard, Vaudreuil-Dorion</t>
+          <t>243 Avenue Saint-Charles, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5173,39 +5173,35 @@
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>http://www.morenointl.com/</t>
-        </is>
-      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>(877) 292-6134</t>
+          <t>(450) 218-4442</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>André Gagnon</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Warehousing / Distribution</t>
+          <t>General Contractor</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5215,12 +5211,12 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$975K-$2.0M</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$98K-$202K</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5229,23 +5225,23 @@
         </is>
       </c>
       <c r="P58" s="5" t="n">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>Category: Warehousing / Distribution | High acquisition fit; priority follow-up</t>
+          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Peinture Jdp Inc</t>
+          <t>Plomberie MALV Inc.</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>190 5e Avenue, Pincourt</t>
+          <t>413 Avenue Saint-Charles, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5256,27 +5252,27 @@
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://www.411habitation.com/peintres/monteregie/pincourt-3/peintres-pincourt.htm</t>
+          <t>https://plomberiemalv.ca/</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>(514) 497-1926</t>
+          <t>(514) 815-9968</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Michel Bouchard</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -5286,7 +5282,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Plumbing Contractor</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -5296,37 +5292,37 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>$1.1M-$2.3M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>$168K-$349K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>10-15 years</t>
         </is>
       </c>
       <c r="P59" s="5" t="n">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Landevel Inc</t>
+          <t>Électvision21 Inc.</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>522 Rue Renaissance, Pincourt</t>
+          <t>3055 Rue du Ravin-Boisé, Vaudreuil-Dorion, QC J7V 5E5, Canada</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5337,27 +5333,27 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>http://www.landevel.com/</t>
+          <t>http://electvision21.com/boutique</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>(514) 425-6660</t>
+          <t>(514) 462-0103</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>Marc Lavoie</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -5391,7 +5387,7 @@
         </is>
       </c>
       <c r="P60" s="5" t="n">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
@@ -5402,12 +5398,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Plomberie CPL Inc.</t>
+          <t>Desmair Inc</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>39 Avenue Pasold, Vaudreuil-Dorion</t>
+          <t>290 Rue Chicoine, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5418,27 +5414,27 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>http://plomberiecpl.ca/</t>
+          <t>http://www.411habitation.com/chauffage-climatisation-ventilation/monteregie/vaudreuil-dorion-1/chauffage-vaudreuil-dorion.htm</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-0791</t>
+          <t>(450) 424-7215</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t>André Lavoie</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Owner not found; manual research required</t>
+          <t>REQ (Registraire des entreprises du Quebec)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -5448,7 +5444,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Plumbing Contractor</t>
+          <t>General Business</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5458,37 +5454,37 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.2M-$2.4M</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$176K-$364K</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>15-20 years</t>
         </is>
       </c>
       <c r="P61" s="5" t="n">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
+          <t>Category: General Business | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Entreprises Hans Gruenwald Inc</t>
+          <t>Plomberie Borny Plumbing</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>3756 Chem. des Sables, Vaudreuil-Dorion, QC J7V 0K1, Canada</t>
+          <t>1263 Bd Virginie-Roy, Notre-Dame-de-l'Île-Perrot, QC J7W 3M5, Canada</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5499,37 +5495,37 @@
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>https://www.gruenwald.ca/</t>
+          <t>https://bornyplumbing.ca/</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>(450) 458-7014</t>
+          <t>(514) 691-3127</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Jean Morin</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>trades</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>General Business</t>
+          <t>Plumbing Contractor</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5539,37 +5535,37 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$168K-$349K</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>5-10 years</t>
         </is>
       </c>
       <c r="P62" s="5" t="n">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
+          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Stemtech Canada, Inc.</t>
+          <t>Deneigement Como</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>440 Rue Aimé-Vincent, Vaudreuil-Dorion</t>
+          <t>1751 Route Harwood, Vaudreuil-Dorion</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5580,27 +5576,27 @@
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>https://www.stemtech.com/ca</t>
+          <t>http://deneigementcomo.ca/</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>(450) 218-6570</t>
+          <t>(514) 647-6375</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Jean Roy</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
+          <t>Owner not found; manual research required</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5620,21 +5616,21 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>$1.0M-$2.1M</t>
+          <t>$1.1M-$2.3M</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>$154K-$319K</t>
+          <t>$165K-$343K</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20-30 years</t>
+          <t>10-15 years</t>
         </is>
       </c>
       <c r="P63" s="5" t="n">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
@@ -5642,1049 +5638,8 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>BRS Express Inc.</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>384 Rue Chicoine, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>https://www.brsexpress.com/</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>(450) 455-5055</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>André Gagnon</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.4M</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>$176K-$364K</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>15-20 years</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>425</v>
-      </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Muscle Mate Equipment Ltd</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>3041 Rue du Plateau, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>https://www.musclemateworks.com/</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>(450) 455-8030</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Luc Lavoie</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>equipment_rental</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Equipment / Maintenance</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>$1.0M-$2.1M</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>$154K-$319K</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v>422</v>
-      </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>Category: Equipment / Maintenance | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Solaris Chem Inc.</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>3650 Boulevard de la Cité-des-Jeunes Suite 101-102, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>http://www.solarischem.com/</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>(579) 217-0260</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Pierre Bouchard</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>$1.0M-$2.1M</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>$154K-$319K</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>421</v>
-      </c>
-      <c r="Q66" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Mécano Plus Vaudreuil Inc</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>1559 Montée Labossière, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>(450) 424-4624</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Pierre Gagnon</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.5M</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>$183K-$380K</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Entrepreneur Michel Levesque Inc</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>243 Avenue Saint-Charles, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>(450) 218-4442</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>General Contractor</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>$975K-$2.0M</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>$98K-$202K</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>419</v>
-      </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Contractor | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Comité Ville en Santé de Pincourt</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>375 Boulevard Cardinal Léger, Pincourt</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>https://www.villepincourt.qc.ca/fr/loisirs-et-culture/developpement-social/comites-citoyens</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Michel Morin</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>$1.0M-$2.1M</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>$154K-$319K</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v>417</v>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Plomberie MALV Inc.</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>413 Avenue Saint-Charles, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>https://plomberiemalv.ca/</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>(514) 815-9968</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Plumbing Contractor</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.4M</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>$176K-$364K</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>10-15 years</t>
-        </is>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>417</v>
-      </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Électvision21 Inc.</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>3055 Rue du Ravin-Boisé, Vaudreuil-Dorion, QC J7V 5E5, Canada</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>http://electvision21.com/boutique</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>(514) 462-0103</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Marc Lavoie</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>$1.0M-$2.1M</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>$154K-$319K</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>20-30 years</t>
-        </is>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v>416</v>
-      </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Desmair Inc</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>290 Rue Chicoine, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>http://www.411habitation.com/chauffage-climatisation-ventilation/monteregie/vaudreuil-dorion-1/chauffage-vaudreuil-dorion.htm</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>(450) 424-7215</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>André Lavoie</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>REQ (Registraire des entreprises du Quebec)</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.4M</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>$176K-$364K</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>15-20 years</t>
-        </is>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>416</v>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Plomberie Borny Plumbing</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>1263 Bd Virginie-Roy, Notre-Dame-de-l'Île-Perrot, QC J7W 3M5, Canada</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>https://bornyplumbing.ca/</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>(514) 691-3127</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>trades</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Plumbing Contractor</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>$1.1M-$2.3M</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>$168K-$349K</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>5-10 years</t>
-        </is>
-      </c>
-      <c r="P73" s="5" t="n">
-        <v>415</v>
-      </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>Category: Plumbing Contractor | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Supermarche Don Quichotte Inc</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>110 Boulevard Don-Quichotte, L'Île-Perrot</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>https://www.iga.net/fr/recherche_de_magasin/magasin/0282?utm_source=google&amp;utm_medium=organic_search&amp;utm_campaign=googlebusinessprofile</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>(514) 453-3027</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.4M</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>$176K-$364K</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>15-20 years</t>
-        </is>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v>414</v>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Deneigement Como</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>1751 Route Harwood, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>http://deneigementcomo.ca/</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>(514) 647-6375</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>$1.1M-$2.3M</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>$165K-$343K</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>10-15 years</t>
-        </is>
-      </c>
-      <c r="P75" s="5" t="n">
-        <v>414</v>
-      </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Lebeau Vitres d'autos Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>245 Avenue Saint-Charles, Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>https://www.lebeau.ca/fr/trouver-centre-de-services/lebeau-vitres-d-autos-vaudreuil?utm_source=google&amp;utm_medium=local&amp;utm_campaign=Lebeau%20vitres%20d'autos%20Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>(450) 424-3876</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Owner not found; manual research required</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>General Business</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>$1.2M-$2.4M</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>$176K-$364K</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>15-20 years</t>
-        </is>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v>414</v>
-      </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>Category: General Business | High acquisition fit; priority follow-up</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q76"/>
+  <autoFilter ref="A1:Q63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -6706,9 +5661,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
@@ -6732,31 +5687,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6768,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6787,7 +5730,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 2026-02-17 22:51</t>
+          <t>Generated: 2026-02-18 10:49</t>
         </is>
       </c>
     </row>
@@ -6805,7 +5748,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -6828,7 +5771,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>462</t>
         </is>
       </c>
     </row>
@@ -6840,7 +5783,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>48/75</t>
+          <t>39/62</t>
         </is>
       </c>
     </row>
@@ -6858,7 +5801,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -6922,7 +5865,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
@@ -6948,7 +5891,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>General Contractor</t>
+          <t>Transportation / Logistics</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -6956,14 +5899,14 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>459</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Transportation / Logistics</t>
+          <t>General Contractor</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
@@ -6971,7 +5914,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -6993,7 +5936,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Roofing Contractor</t>
+          <t>Automotive Services</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
@@ -7001,14 +5944,14 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>541</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Automotive Services</t>
+          <t>Roofing Contractor</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
@@ -7016,7 +5959,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -7038,7 +5981,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Equipment / Maintenance</t>
+          <t>Cleaning Services</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -7046,14 +5989,14 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>450</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Accounting / Financial Services</t>
+          <t>Equipment / Maintenance</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
@@ -7061,14 +6004,14 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>422</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Cleaning Services</t>
+          <t>Precision Manufacturing</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
@@ -7076,14 +6019,14 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>489</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Precision Manufacturing</t>
+          <t>Metal Fabrication</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -7091,14 +6034,14 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>487</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Metal Fabrication</t>
+          <t>Light Manufacturing</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
@@ -7106,14 +6049,14 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>502</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Light Manufacturing</t>
+          <t>Wholesale / Distribution</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
@@ -7121,66 +6064,61 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>502</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Wholesale / Distribution</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
           <t>441</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Industry Breakdown</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Industry Breakdown</t>
-        </is>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>landscaping</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
@@ -7190,7 +6128,7 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>landscaping</t>
+          <t>cleaning_services</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
@@ -7200,7 +6138,7 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>cleaning_services</t>
+          <t>wholesale</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
@@ -7210,7 +6148,7 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>wholesale</t>
+          <t>equipment_rental</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
@@ -7220,20 +6158,10 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>equipment_rental</t>
+          <t>trades</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>trades</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="n">
         <v>1</v>
       </c>
     </row>
